--- a/pesaje/analytica/Report/ActaConformidad-Export-Pesaje-Base.xlsx
+++ b/pesaje/analytica/Report/ActaConformidad-Export-Pesaje-Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C86839-7414-4213-BAD7-EF30E06A9776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB4B284-74B5-49D7-BB0B-5DAFB4D248B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>Exportado por:</t>
   </si>
   <si>
-    <t>Nª ACTA</t>
-  </si>
-  <si>
     <t>PROVEEDOR</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>,</t>
+  </si>
+  <si>
+    <t>N° ACTA</t>
   </si>
 </sst>
 </file>
@@ -211,12 +211,6 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -241,6 +235,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -529,244 +529,244 @@
   <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="37.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="42.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.77734375" style="3" customWidth="1"/>
-    <col min="8" max="9" width="28.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="24.77734375" style="3" customWidth="1"/>
-    <col min="11" max="12" width="24.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.77734375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="28.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.77734375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="24.6640625" style="1" customWidth="1"/>
     <col min="16371" max="16384" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
     </row>
     <row r="2" spans="1:49" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
     </row>
     <row r="3" spans="1:49" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
     </row>
     <row r="4" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
     </row>
     <row r="5" spans="1:49" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:49" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:49" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:49" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:49" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="K8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>15</v>
       </c>
       <c r="AJ8"/>
       <c r="AK8"/>
@@ -783,7 +783,7 @@
       <c r="AV8"/>
       <c r="AW8"/>
     </row>
-    <row r="9" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="AJ9"/>
       <c r="AK9"/>
       <c r="AL9"/>
@@ -800,8 +800,8 @@
       <c r="AW9"/>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="F11" s="3" t="s">
-        <v>16</v>
+      <c r="F11" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
